--- a/salidas/empresas/PGR.xlsx
+++ b/salidas/empresas/PGR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>13.63597869873047</v>
+        <v>13.63597965240479</v>
       </c>
       <c r="C2" t="n">
         <v>26.26000022888184</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>13.9488353729248</v>
+        <v>13.94883346557617</v>
       </c>
       <c r="C3" t="n">
         <v>26.86249923706055</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>13.5386266708374</v>
+        <v>13.53862762451172</v>
       </c>
       <c r="C4" t="n">
         <v>26.06500053405762</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>14.09310150146484</v>
+        <v>14.09310626983643</v>
       </c>
       <c r="C5" t="n">
         <v>27.13249969482422</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>14.20608043670654</v>
+        <v>14.20607566833496</v>
       </c>
       <c r="C6" t="n">
         <v>27.35000038146973</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>13.36901664733887</v>
+        <v>13.3690128326416</v>
       </c>
       <c r="C7" t="n">
         <v>25.70999908447266</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>12.57862567901611</v>
+        <v>12.57862758636475</v>
       </c>
       <c r="C8" t="n">
         <v>24.19000053405762</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>12.78662490844727</v>
+        <v>12.7866268157959</v>
       </c>
       <c r="C9" t="n">
         <v>24.59000015258789</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>12.76542091369629</v>
+        <v>12.76542282104492</v>
       </c>
       <c r="C10" t="n">
         <v>24.54000091552734</v>
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>11.73024463653564</v>
+        <v>11.73024749755859</v>
       </c>
       <c r="C12" t="n">
         <v>22.54999923706055</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>12.60400009155273</v>
+        <v>12.60400104522705</v>
       </c>
       <c r="C13" t="n">
         <v>24.21999931335449</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>12.0679931640625</v>
+        <v>12.06799507141113</v>
       </c>
       <c r="C14" t="n">
         <v>23.19000053405762</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>11.93789672851562</v>
+        <v>11.93789482116699</v>
       </c>
       <c r="C15" t="n">
         <v>22.94000053405762</v>
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>12.0055456161499</v>
+        <v>12.00554656982422</v>
       </c>
       <c r="C17" t="n">
         <v>23.06999969482422</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>11.99514102935791</v>
+        <v>11.99513816833496</v>
       </c>
       <c r="C18" t="n">
         <v>23.04999923706055</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>12.45308780670166</v>
+        <v>12.45308494567871</v>
       </c>
       <c r="C19" t="n">
         <v>23.93000030517578</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>10.9179162979126</v>
+        <v>10.91791820526123</v>
       </c>
       <c r="C20" t="n">
         <v>20.97999954223633</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>11.61703300476074</v>
+        <v>11.61702823638916</v>
       </c>
       <c r="C21" t="n">
         <v>20.34000015258789</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>11.08587074279785</v>
+        <v>11.0858678817749</v>
       </c>
       <c r="C22" t="n">
         <v>19.40999984741211</v>
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>10.50901126861572</v>
+        <v>10.50901222229004</v>
       </c>
       <c r="C24" t="n">
         <v>18.39999961853027</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>10.94308376312256</v>
+        <v>10.94308567047119</v>
       </c>
       <c r="C25" t="n">
         <v>19.15999984741211</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>10.6781063079834</v>
+        <v>10.67810440063477</v>
       </c>
       <c r="C26" t="n">
         <v>18.54999923706055</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>10.5514669418335</v>
+        <v>10.55146789550781</v>
       </c>
       <c r="C27" t="n">
         <v>18.32999992370605</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>9.250524520874023</v>
+        <v>9.250520706176758</v>
       </c>
       <c r="C28" t="n">
         <v>16.06999969482422</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>10.47087860107422</v>
+        <v>10.47088050842285</v>
       </c>
       <c r="C29" t="n">
         <v>18.19000053405762</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>11.54732513427734</v>
+        <v>11.54732322692871</v>
       </c>
       <c r="C30" t="n">
         <v>20.05999946594238</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>10.77596855163574</v>
+        <v>10.77596378326416</v>
       </c>
       <c r="C31" t="n">
         <v>18.71999931335449</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>11.65669536590576</v>
+        <v>11.65669441223145</v>
       </c>
       <c r="C32" t="n">
         <v>20.25</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>10.63205718994141</v>
+        <v>10.63205814361572</v>
       </c>
       <c r="C33" t="n">
         <v>18.46999931335449</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>10.01611995697021</v>
+        <v>10.0161247253418</v>
       </c>
       <c r="C34" t="n">
         <v>17.39999961853027</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>8.214371681213379</v>
+        <v>8.214370727539062</v>
       </c>
       <c r="C35" t="n">
         <v>14.27000045776367</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>8.646101951599121</v>
+        <v>8.646100044250488</v>
       </c>
       <c r="C36" t="n">
         <v>15.02000045776367</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>8.525216102600098</v>
+        <v>8.52521800994873</v>
       </c>
       <c r="C37" t="n">
         <v>14.8100004196167</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>6.994015216827393</v>
+        <v>6.994019508361816</v>
       </c>
       <c r="C38" t="n">
         <v>12.14999961853027</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>6.660145282745361</v>
+        <v>6.660144805908203</v>
       </c>
       <c r="C39" t="n">
         <v>11.56999969482422</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>7.736591815948486</v>
+        <v>7.736593723297119</v>
       </c>
       <c r="C40" t="n">
         <v>13.4399995803833</v>
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>9.285059928894043</v>
+        <v>9.285060882568359</v>
       </c>
       <c r="C42" t="n">
         <v>16.1299991607666</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>8.697908401489258</v>
+        <v>8.697907447814941</v>
       </c>
       <c r="C43" t="n">
         <v>15.10999965667725</v>
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>9.509557723999023</v>
+        <v>9.509561538696289</v>
       </c>
       <c r="C45" t="n">
         <v>16.52000045776367</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>9.544098854064941</v>
+        <v>9.544100761413574</v>
       </c>
       <c r="C46" t="n">
         <v>16.57999992370605</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>9.210227012634277</v>
+        <v>9.210229873657227</v>
       </c>
       <c r="C47" t="n">
         <v>16</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>9.653471946716309</v>
+        <v>9.653470039367676</v>
       </c>
       <c r="C48" t="n">
         <v>16.77000045776367</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>10.35574913024902</v>
+        <v>10.35574722290039</v>
       </c>
       <c r="C49" t="n">
         <v>17.98999977111816</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>9.635950088500977</v>
+        <v>9.63594913482666</v>
       </c>
       <c r="C50" t="n">
         <v>16.57999992370605</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>9.967222213745117</v>
+        <v>9.967225074768066</v>
       </c>
       <c r="C51" t="n">
         <v>17.14999961853027</v>
@@ -1474,7 +1486,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>11.6758918762207</v>
+        <v>11.67588901519775</v>
       </c>
       <c r="C53" t="n">
         <v>20.09000015258789</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>11.3853006362915</v>
+        <v>11.38529968261719</v>
       </c>
       <c r="C54" t="n">
         <v>19.59000015258789</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>10.87967681884766</v>
+        <v>10.87967491149902</v>
       </c>
       <c r="C55" t="n">
         <v>18.71999931335449</v>
@@ -1574,7 +1586,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>11.50734806060791</v>
+        <v>11.50734615325928</v>
       </c>
       <c r="C57" t="n">
         <v>19.79999923706055</v>
@@ -1624,7 +1636,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>12.29775238037109</v>
+        <v>12.29775524139404</v>
       </c>
       <c r="C59" t="n">
         <v>21.15999984741211</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>11.82118797302246</v>
+        <v>11.8211841583252</v>
       </c>
       <c r="C60" t="n">
         <v>20.34000015258789</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>12.13274383544922</v>
+        <v>12.13274002075195</v>
       </c>
       <c r="C61" t="n">
         <v>19.8700008392334</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>12.34398078918457</v>
+        <v>12.3439769744873</v>
       </c>
       <c r="C62" t="n">
         <v>19.80999946594238</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>12.97956275939941</v>
+        <v>12.97955799102783</v>
       </c>
       <c r="C63" t="n">
         <v>20.82999992370605</v>
@@ -1774,11 +1786,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>13.1664867401123</v>
+        <v>13.16648960113525</v>
       </c>
       <c r="C64" t="n">
         <v>21.1299991607666</v>
@@ -1803,11 +1815,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>13.67122268676758</v>
+        <v>13.67121982574463</v>
       </c>
       <c r="C65" t="n">
         <v>21.94000053405762</v>
@@ -1832,11 +1844,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>13.49051666259766</v>
+        <v>13.49051570892334</v>
       </c>
       <c r="C66" t="n">
         <v>21.64999961853027</v>
@@ -1861,11 +1873,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>13.32227325439453</v>
+        <v>13.32227802276611</v>
       </c>
       <c r="C67" t="n">
         <v>21.3799991607666</v>
@@ -1890,11 +1902,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>12.26297283172607</v>
+        <v>12.26297473907471</v>
       </c>
       <c r="C68" t="n">
         <v>19.68000030517578</v>
@@ -1919,11 +1931,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>11.95141410827637</v>
+        <v>11.95141696929932</v>
       </c>
       <c r="C69" t="n">
         <v>19.18000030517578</v>
@@ -1948,11 +1960,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>11.06658458709717</v>
+        <v>11.06658554077148</v>
       </c>
       <c r="C70" t="n">
         <v>17.76000022888184</v>
@@ -1977,11 +1989,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>11.84548091888428</v>
+        <v>11.84548282623291</v>
       </c>
       <c r="C71" t="n">
         <v>19.01000022888184</v>
@@ -2006,11 +2018,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>11.7520112991333</v>
+        <v>11.75201416015625</v>
       </c>
       <c r="C72" t="n">
         <v>18.86000061035156</v>
@@ -2035,11 +2047,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>12.15704441070557</v>
+        <v>12.1570463180542</v>
       </c>
       <c r="C73" t="n">
         <v>19.51000022888184</v>
@@ -2064,11 +2076,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>12.89041423797607</v>
+        <v>12.89041519165039</v>
       </c>
       <c r="C74" t="n">
         <v>20.28000068664551</v>
@@ -2093,11 +2105,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>13.61502456665039</v>
+        <v>13.61502265930176</v>
       </c>
       <c r="C75" t="n">
         <v>21.42000007629395</v>
@@ -2122,11 +2134,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>14.73372459411621</v>
+        <v>14.73371982574463</v>
       </c>
       <c r="C76" t="n">
         <v>23.18000030517578</v>
@@ -2151,7 +2163,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2180,11 +2192,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>13.81206607818604</v>
+        <v>13.81206703186035</v>
       </c>
       <c r="C78" t="n">
         <v>21.72999954223633</v>
@@ -2209,11 +2221,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>13.24001026153564</v>
+        <v>13.24000549316406</v>
       </c>
       <c r="C79" t="n">
         <v>20.82999992370605</v>
@@ -2238,7 +2250,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2267,11 +2279,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>12.4136962890625</v>
+        <v>12.41370010375977</v>
       </c>
       <c r="C81" t="n">
         <v>19.53000068664551</v>
@@ -2296,11 +2308,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>13.18280029296875</v>
+        <v>13.18279838562012</v>
       </c>
       <c r="C82" t="n">
         <v>20.73999977111816</v>
@@ -2325,11 +2337,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>14.17437171936035</v>
+        <v>14.17437553405762</v>
       </c>
       <c r="C83" t="n">
         <v>22.29999923706055</v>
@@ -2354,7 +2366,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2383,11 +2395,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>14.03397464752197</v>
+        <v>14.03397846221924</v>
       </c>
       <c r="C85" t="n">
         <v>21.10000038146973</v>
@@ -2412,7 +2424,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2441,11 +2453,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>16.4059886932373</v>
+        <v>16.40599250793457</v>
       </c>
       <c r="C87" t="n">
         <v>24.36000061035156</v>
@@ -2470,7 +2482,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2499,11 +2511,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>17.0323314666748</v>
+        <v>17.03232765197754</v>
       </c>
       <c r="C89" t="n">
         <v>25.29000091552734</v>
@@ -2528,7 +2540,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2557,11 +2569,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>17.1198787689209</v>
+        <v>17.1198844909668</v>
       </c>
       <c r="C91" t="n">
         <v>25.42000007629395</v>
@@ -2586,7 +2598,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2615,11 +2627,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>16.88416481018066</v>
+        <v>16.8841609954834</v>
       </c>
       <c r="C93" t="n">
         <v>25.06999969482422</v>
@@ -2644,11 +2656,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>18.33888053894043</v>
+        <v>18.3388843536377</v>
       </c>
       <c r="C94" t="n">
         <v>27.22999954223633</v>
@@ -2673,11 +2685,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>17.49029541015625</v>
+        <v>17.49029922485352</v>
       </c>
       <c r="C95" t="n">
         <v>25.96999931335449</v>
@@ -2702,7 +2714,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2731,11 +2743,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>18.36582183837891</v>
+        <v>18.36581993103027</v>
       </c>
       <c r="C97" t="n">
         <v>27.27000045776367</v>
@@ -2760,11 +2772,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>16.65431022644043</v>
+        <v>16.6543083190918</v>
       </c>
       <c r="C98" t="n">
         <v>23.23999977111816</v>
@@ -2789,7 +2801,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2818,11 +2830,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>17.35659980773926</v>
+        <v>17.35659599304199</v>
       </c>
       <c r="C100" t="n">
         <v>24.21999931335449</v>
@@ -2847,11 +2859,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>17.37809562683105</v>
+        <v>17.37809753417969</v>
       </c>
       <c r="C101" t="n">
         <v>24.25</v>
@@ -2876,11 +2888,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>17.93706321716309</v>
+        <v>17.93706130981445</v>
       </c>
       <c r="C102" t="n">
         <v>25.03000068664551</v>
@@ -2905,11 +2917,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>18.17354583740234</v>
+        <v>18.17355346679688</v>
       </c>
       <c r="C103" t="n">
         <v>25.36000061035156</v>
@@ -2934,11 +2946,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>16.79763793945312</v>
+        <v>16.79763221740723</v>
       </c>
       <c r="C104" t="n">
         <v>23.44000053405762</v>
@@ -2963,7 +2975,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -2992,11 +3004,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>18.1162166595459</v>
+        <v>18.11622619628906</v>
       </c>
       <c r="C106" t="n">
         <v>25.28000068664551</v>
@@ -3021,11 +3033,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>18.92600250244141</v>
+        <v>18.92600440979004</v>
       </c>
       <c r="C107" t="n">
         <v>26.40999984741211</v>
@@ -3050,11 +3062,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>19.52079963684082</v>
+        <v>19.52079772949219</v>
       </c>
       <c r="C108" t="n">
         <v>27.23999977111816</v>
@@ -3079,11 +3091,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>19.34163856506348</v>
+        <v>19.34164237976074</v>
       </c>
       <c r="C109" t="n">
         <v>26.98999977111816</v>
@@ -3108,11 +3120,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>18.59635925292969</v>
+        <v>18.59635543823242</v>
       </c>
       <c r="C110" t="n">
         <v>25.95000076293945</v>
@@ -3137,11 +3149,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>19.61656761169434</v>
+        <v>19.61656379699707</v>
       </c>
       <c r="C111" t="n">
         <v>26.64999961853027</v>
@@ -3166,7 +3178,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3195,7 +3207,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3224,11 +3236,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>20.12445831298828</v>
+        <v>20.12446022033691</v>
       </c>
       <c r="C114" t="n">
         <v>27.34000015258789</v>
@@ -3253,11 +3265,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>20.48514175415039</v>
+        <v>20.48513984680176</v>
       </c>
       <c r="C115" t="n">
         <v>27.82999992370605</v>
@@ -3282,11 +3294,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>22.45047378540039</v>
+        <v>22.45047569274902</v>
       </c>
       <c r="C116" t="n">
         <v>30.5</v>
@@ -3311,11 +3323,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>22.05299377441406</v>
+        <v>22.0529899597168</v>
       </c>
       <c r="C117" t="n">
         <v>29.95999908447266</v>
@@ -3340,11 +3352,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>22.55352783203125</v>
+        <v>22.55352592468262</v>
       </c>
       <c r="C118" t="n">
         <v>30.63999938964844</v>
@@ -3369,11 +3381,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>24.38636779785156</v>
+        <v>24.38637924194336</v>
       </c>
       <c r="C119" t="n">
         <v>33.13000106811523</v>
@@ -3398,11 +3410,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>22.6860237121582</v>
+        <v>22.68602180480957</v>
       </c>
       <c r="C120" t="n">
         <v>30.81999969482422</v>
@@ -3427,7 +3439,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3456,11 +3468,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>23.00254058837891</v>
+        <v>23.00253677368164</v>
       </c>
       <c r="C122" t="n">
         <v>31.25</v>
@@ -3485,11 +3497,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>24.18289184570312</v>
+        <v>24.18289566040039</v>
       </c>
       <c r="C123" t="n">
         <v>31.92000007629395</v>
@@ -3514,11 +3526,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>26.62239646911621</v>
+        <v>26.62239456176758</v>
       </c>
       <c r="C124" t="n">
         <v>35.13999938964844</v>
@@ -3543,11 +3555,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>24.69806861877441</v>
+        <v>24.69806480407715</v>
       </c>
       <c r="C125" t="n">
         <v>32.59999847412109</v>
@@ -3572,11 +3584,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>25.22839546203613</v>
+        <v>25.2283935546875</v>
       </c>
       <c r="C126" t="n">
         <v>33.29999923706055</v>
@@ -3601,11 +3613,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>25.37991523742676</v>
+        <v>25.37991333007812</v>
       </c>
       <c r="C127" t="n">
         <v>33.5</v>
@@ -3630,11 +3642,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>24.62987899780273</v>
+        <v>24.6298828125</v>
       </c>
       <c r="C128" t="n">
         <v>32.5099983215332</v>
@@ -3659,7 +3671,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3688,11 +3700,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>23.86469841003418</v>
+        <v>23.86469650268555</v>
       </c>
       <c r="C130" t="n">
         <v>31.5</v>
@@ -3717,11 +3729,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>23.87227249145508</v>
+        <v>23.87227630615234</v>
       </c>
       <c r="C131" t="n">
         <v>31.51000022888184</v>
@@ -3746,11 +3758,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>25.22839546203613</v>
+        <v>25.2283935546875</v>
       </c>
       <c r="C132" t="n">
         <v>33.29999923706055</v>
@@ -3775,11 +3787,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>26.89513778686523</v>
+        <v>26.89513969421387</v>
       </c>
       <c r="C133" t="n">
         <v>35.5</v>
@@ -3804,11 +3816,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>28.36490058898926</v>
+        <v>28.36489677429199</v>
       </c>
       <c r="C134" t="n">
         <v>37.43999862670898</v>
@@ -3833,11 +3845,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>30.23305702209473</v>
+        <v>30.23304557800293</v>
       </c>
       <c r="C135" t="n">
         <v>39.18000030517578</v>
@@ -3862,11 +3874,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>30.23305702209473</v>
+        <v>30.23304557800293</v>
       </c>
       <c r="C136" t="n">
         <v>39.18000030517578</v>
@@ -3891,11 +3903,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>30.64973258972168</v>
+        <v>30.64974021911621</v>
       </c>
       <c r="C137" t="n">
         <v>39.72000122070312</v>
@@ -3920,11 +3932,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>32.74089431762695</v>
+        <v>32.74090957641602</v>
       </c>
       <c r="C138" t="n">
         <v>42.43000030517578</v>
@@ -3949,11 +3961,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>34.02182769775391</v>
+        <v>34.02183151245117</v>
       </c>
       <c r="C139" t="n">
         <v>44.09000015258789</v>
@@ -3978,11 +3990,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>36.36761856079102</v>
+        <v>36.36762619018555</v>
       </c>
       <c r="C140" t="n">
         <v>47.13000106811523</v>
@@ -4007,11 +4019,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>35.86606597900391</v>
+        <v>35.86605453491211</v>
       </c>
       <c r="C141" t="n">
         <v>46.47999954223633</v>
@@ -4036,11 +4048,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>37.36304092407227</v>
+        <v>37.36305236816406</v>
       </c>
       <c r="C142" t="n">
         <v>48.41999816894531</v>
@@ -4065,11 +4077,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>37.54053497314453</v>
+        <v>37.54052734375</v>
       </c>
       <c r="C143" t="n">
         <v>48.65000152587891</v>
@@ -4094,11 +4106,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>41.03609466552734</v>
+        <v>41.03608703613281</v>
       </c>
       <c r="C144" t="n">
         <v>53.18000030517578</v>
@@ -4123,11 +4135,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>43.45904541015625</v>
+        <v>43.45904922485352</v>
       </c>
       <c r="C145" t="n">
         <v>56.31999969482422</v>
@@ -4152,11 +4164,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>41.74599456787109</v>
+        <v>41.74597930908203</v>
       </c>
       <c r="C146" t="n">
         <v>54.09999847412109</v>
@@ -4181,7 +4193,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4210,7 +4222,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4239,7 +4251,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4268,11 +4280,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>48.92889404296875</v>
+        <v>48.92890548706055</v>
       </c>
       <c r="C150" t="n">
         <v>62.09000015258789</v>
@@ -4297,11 +4309,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>46.61209487915039</v>
+        <v>46.61209106445312</v>
       </c>
       <c r="C151" t="n">
         <v>59.15000152587891</v>
@@ -4326,11 +4338,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>47.28979110717773</v>
+        <v>47.28980255126953</v>
       </c>
       <c r="C152" t="n">
         <v>60.0099983215332</v>
@@ -4355,11 +4367,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>53.21579360961914</v>
+        <v>53.21580505371094</v>
       </c>
       <c r="C153" t="n">
         <v>67.52999877929688</v>
@@ -4384,11 +4396,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>55.98178863525391</v>
+        <v>55.98179244995117</v>
       </c>
       <c r="C154" t="n">
         <v>71.04000091552734</v>
@@ -4413,11 +4425,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>54.92583084106445</v>
+        <v>54.92582702636719</v>
       </c>
       <c r="C155" t="n">
         <v>69.69999694824219</v>
@@ -4442,7 +4454,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4471,7 +4483,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4500,11 +4512,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>53.02666091918945</v>
+        <v>53.02666854858398</v>
       </c>
       <c r="C158" t="n">
         <v>67.29000091552734</v>
@@ -4529,7 +4541,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4558,11 +4570,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>59.01403427124023</v>
+        <v>59.01402282714844</v>
       </c>
       <c r="C160" t="n">
         <v>72.08999633789062</v>
@@ -4587,11 +4599,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>64.06256866455078</v>
+        <v>64.06254577636719</v>
       </c>
       <c r="C161" t="n">
         <v>78.15000152587891</v>
@@ -4616,7 +4628,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4645,11 +4657,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>65.52172088623047</v>
+        <v>65.52169036865234</v>
       </c>
       <c r="C163" t="n">
         <v>79.93000030517578</v>
@@ -4674,11 +4686,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>66.46285247802734</v>
+        <v>66.46284484863281</v>
       </c>
       <c r="C164" t="n">
         <v>80.98000335693359</v>
@@ -4703,11 +4715,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>62.21145248413086</v>
+        <v>62.21146774291992</v>
       </c>
       <c r="C165" t="n">
         <v>75.80000305175781</v>
@@ -4732,11 +4744,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>63.40151977539062</v>
+        <v>63.40151214599609</v>
       </c>
       <c r="C166" t="n">
         <v>77.25</v>
@@ -4761,7 +4773,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4790,11 +4802,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>60.03408050537109</v>
+        <v>60.03407287597656</v>
       </c>
       <c r="C168" t="n">
         <v>73.05000305175781</v>
@@ -4819,11 +4831,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>59.49167633056641</v>
+        <v>59.49167251586914</v>
       </c>
       <c r="C169" t="n">
         <v>72.38999938964844</v>
@@ -4848,11 +4860,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>68.43822479248047</v>
+        <v>68.43820953369141</v>
       </c>
       <c r="C170" t="n">
         <v>80.69000244140625</v>
@@ -4877,11 +4889,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>62.05155563354492</v>
+        <v>62.05154800415039</v>
       </c>
       <c r="C171" t="n">
         <v>73.16000366210938</v>
@@ -4906,11 +4918,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>62.62829208374023</v>
+        <v>62.6282958984375</v>
       </c>
       <c r="C172" t="n">
         <v>73.83999633789062</v>
@@ -4935,11 +4947,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>65.64938354492188</v>
+        <v>65.64939880371094</v>
       </c>
       <c r="C173" t="n">
         <v>77.30000305175781</v>
@@ -4964,11 +4976,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>65.97212982177734</v>
+        <v>65.97209930419922</v>
       </c>
       <c r="C174" t="n">
         <v>77.68000030517578</v>
@@ -4993,7 +5005,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5022,11 +5034,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>76.82095336914062</v>
+        <v>76.82096099853516</v>
       </c>
       <c r="C176" t="n">
         <v>90.33999633789062</v>
@@ -5051,11 +5063,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>80.81761932373047</v>
+        <v>80.81761169433594</v>
       </c>
       <c r="C177" t="n">
         <v>95.04000091552734</v>
@@ -5080,11 +5092,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>80.50299835205078</v>
+        <v>80.50300598144531</v>
       </c>
       <c r="C178" t="n">
         <v>94.66999816894531</v>
@@ -5109,11 +5121,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>78.22902679443359</v>
+        <v>78.22901153564453</v>
       </c>
       <c r="C179" t="n">
         <v>91.90000152587891</v>
@@ -5138,11 +5150,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>74.15158081054688</v>
+        <v>74.15157318115234</v>
       </c>
       <c r="C180" t="n">
         <v>87.11000061035156</v>
@@ -5167,11 +5179,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>84.17070007324219</v>
+        <v>84.17066955566406</v>
       </c>
       <c r="C181" t="n">
         <v>98.87999725341797</v>
@@ -5196,11 +5208,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>77.84436798095703</v>
+        <v>77.84437561035156</v>
       </c>
       <c r="C182" t="n">
         <v>87.19000244140625</v>
@@ -5225,11 +5237,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>76.73728942871094</v>
+        <v>76.73728179931641</v>
       </c>
       <c r="C183" t="n">
         <v>85.94999694824219</v>
@@ -5254,11 +5266,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>85.36186218261719</v>
+        <v>85.36183929443359</v>
       </c>
       <c r="C184" t="n">
         <v>95.61000061035156</v>
@@ -5283,11 +5295,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>90.03507995605469</v>
+        <v>90.03507232666016</v>
       </c>
       <c r="C185" t="n">
         <v>100.7399978637695</v>
@@ -5312,7 +5324,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5341,7 +5353,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5370,11 +5382,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>85.134033203125</v>
+        <v>85.13405609130859</v>
       </c>
       <c r="C188" t="n">
         <v>95.16000366210938</v>
@@ -5399,11 +5411,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>86.18971252441406</v>
+        <v>86.18973541259766</v>
       </c>
       <c r="C189" t="n">
         <v>96.33999633789062</v>
@@ -5428,11 +5440,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>80.86660003662109</v>
+        <v>80.86662292480469</v>
       </c>
       <c r="C190" t="n">
         <v>90.38999938964844</v>
@@ -5457,11 +5469,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>84.97666168212891</v>
+        <v>84.97665405273438</v>
       </c>
       <c r="C191" t="n">
         <v>94.87999725341797</v>
@@ -5486,11 +5498,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>83.23916625976562</v>
+        <v>83.23915863037109</v>
       </c>
       <c r="C192" t="n">
         <v>92.94000244140625</v>
@@ -5515,11 +5527,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>93.29403686523438</v>
+        <v>93.29402160644531</v>
       </c>
       <c r="C193" t="n">
         <v>102.6500015258789</v>
@@ -5544,11 +5556,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>98.85233306884766</v>
+        <v>98.85234069824219</v>
       </c>
       <c r="C194" t="n">
         <v>108.6600036621094</v>
@@ -5573,11 +5585,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>96.36876678466797</v>
+        <v>96.36873626708984</v>
       </c>
       <c r="C195" t="n">
         <v>105.9300003051758</v>
@@ -5602,11 +5614,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>103.7012405395508</v>
+        <v>103.7012557983398</v>
       </c>
       <c r="C196" t="n">
         <v>113.9899978637695</v>
@@ -5631,11 +5643,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>97.75525665283203</v>
+        <v>97.7552490234375</v>
       </c>
       <c r="C197" t="n">
         <v>107.3600006103516</v>
@@ -5660,7 +5672,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5689,11 +5701,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>105.8681182861328</v>
+        <v>105.8681259155273</v>
       </c>
       <c r="C199" t="n">
         <v>116.2699966430664</v>
@@ -5718,11 +5730,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>104.8558959960938</v>
+        <v>104.8558883666992</v>
       </c>
       <c r="C200" t="n">
         <v>115.0599975585938</v>
@@ -5747,11 +5759,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>111.7727737426758</v>
+        <v>111.7727813720703</v>
       </c>
       <c r="C201" t="n">
         <v>122.6500015258789</v>
@@ -5776,7 +5788,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5805,7 +5817,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5834,11 +5846,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>120.5287857055664</v>
+        <v>120.5287933349609</v>
       </c>
       <c r="C204" t="n">
         <v>132.1499938964844</v>
@@ -5863,11 +5875,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>118.3033676147461</v>
+        <v>118.303352355957</v>
       </c>
       <c r="C205" t="n">
         <v>129.7100067138672</v>
@@ -5892,11 +5904,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>124.4542999267578</v>
+        <v>124.4542770385742</v>
       </c>
       <c r="C206" t="n">
         <v>136.3500061035156</v>
@@ -5921,11 +5933,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>130.9987335205078</v>
+        <v>130.9987487792969</v>
       </c>
       <c r="C207" t="n">
         <v>143.5200042724609</v>
@@ -5950,7 +5962,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5979,11 +5991,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>124.5862579345703</v>
+        <v>124.5862731933594</v>
       </c>
       <c r="C209" t="n">
         <v>136.3999938964844</v>
@@ -6008,11 +6020,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>116.8315963745117</v>
+        <v>116.8316116333008</v>
       </c>
       <c r="C210" t="n">
         <v>127.9100036621094</v>
@@ -6037,11 +6049,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>120.9052810668945</v>
+        <v>120.9053039550781</v>
       </c>
       <c r="C211" t="n">
         <v>132.3699951171875</v>
@@ -6066,11 +6078,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>115.1563720703125</v>
+        <v>115.156364440918</v>
       </c>
       <c r="C212" t="n">
         <v>125.9800033569336</v>
@@ -6095,11 +6107,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>122.0028610229492</v>
+        <v>122.0028533935547</v>
       </c>
       <c r="C213" t="n">
         <v>133.4700012207031</v>
@@ -6124,11 +6136,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>127.3319778442383</v>
+        <v>127.3319625854492</v>
       </c>
       <c r="C214" t="n">
         <v>139.3000030517578</v>
@@ -6153,11 +6165,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>144.6113586425781</v>
+        <v>144.611328125</v>
       </c>
       <c r="C215" t="n">
         <v>158.0899963378906</v>
@@ -6182,11 +6194,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>150.0449066162109</v>
+        <v>150.0449523925781</v>
       </c>
       <c r="C216" t="n">
         <v>164.0299987792969</v>
@@ -6211,11 +6223,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>145.6999206542969</v>
+        <v>145.6998596191406</v>
       </c>
       <c r="C217" t="n">
         <v>159.2799987792969</v>
@@ -6240,11 +6252,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>163.8724365234375</v>
+        <v>163.8724212646484</v>
       </c>
       <c r="C218" t="n">
         <v>178.25</v>
@@ -6269,11 +6281,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>174.2701568603516</v>
+        <v>174.2701416015625</v>
       </c>
       <c r="C219" t="n">
         <v>189.5599975585938</v>
@@ -6298,7 +6310,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6327,11 +6339,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>191.5438079833984</v>
+        <v>191.5438232421875</v>
       </c>
       <c r="C221" t="n">
         <v>208.25</v>
@@ -6356,7 +6368,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6385,11 +6397,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>191.0471496582031</v>
+        <v>191.0471801757812</v>
       </c>
       <c r="C223" t="n">
         <v>207.7100067138672</v>
@@ -6414,7 +6426,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6443,11 +6455,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>232.0780029296875</v>
+        <v>232.0780334472656</v>
       </c>
       <c r="C225" t="n">
         <v>252.1999969482422</v>
@@ -6472,7 +6484,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6501,7 +6513,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6530,11 +6542,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>247.5244750976562</v>
+        <v>247.5244903564453</v>
       </c>
       <c r="C228" t="n">
         <v>268.8800048828125</v>
@@ -6559,11 +6571,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>220.5791931152344</v>
+        <v>220.5792236328125</v>
       </c>
       <c r="C229" t="n">
         <v>239.6100006103516</v>
@@ -6588,7 +6600,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6617,11 +6629,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>264.5991516113281</v>
+        <v>264.5991821289062</v>
       </c>
       <c r="C231" t="n">
         <v>282</v>
@@ -6646,7 +6658,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6675,11 +6687,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>264.44921875</v>
+        <v>264.4492492675781</v>
       </c>
       <c r="C233" t="n">
         <v>281.739990234375</v>
@@ -6704,11 +6716,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>267.4434814453125</v>
+        <v>267.4434509277344</v>
       </c>
       <c r="C234" t="n">
         <v>284.9299926757812</v>
@@ -6733,7 +6745,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6762,11 +6774,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>227.2738342285156</v>
+        <v>227.2738494873047</v>
       </c>
       <c r="C236" t="n">
         <v>242.0399932861328</v>
@@ -6791,7 +6803,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6820,7 +6832,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6849,11 +6861,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>193.5110473632812</v>
+        <v>193.5110626220703</v>
       </c>
       <c r="C239" t="n">
         <v>206</v>
@@ -6878,11 +6890,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>214.9194030761719</v>
+        <v>214.9193878173828</v>
       </c>
       <c r="C240" t="n">
         <v>228.7899932861328</v>
@@ -6907,11 +6919,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>213.9142761230469</v>
+        <v>213.9142608642578</v>
       </c>
       <c r="C241" t="n">
         <v>227.7200012207031</v>
@@ -6936,7 +6948,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6965,7 +6977,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6994,7 +7006,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7023,7 +7035,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7052,7 +7064,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7081,7 +7093,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7110,7 +7122,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7139,7 +7151,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7168,32 +7180,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>203.1300048828125</v>
+        <v>202.1699981689453</v>
       </c>
       <c r="C250" t="n">
-        <v>203.1300048828125</v>
+        <v>202.1699981689453</v>
       </c>
       <c r="D250" t="n">
-        <v>41472000</v>
+        <v>46555500</v>
       </c>
       <c r="E250" t="n">
         <v>19.93</v>
       </c>
       <c r="F250" t="n">
-        <v>10.19217284911252</v>
+        <v>10.14400392217488</v>
       </c>
       <c r="G250" t="n">
         <v>581371770</v>
       </c>
       <c r="H250" t="n">
-        <v>118094050478.8293</v>
+        <v>117535929676.3765</v>
       </c>
       <c r="I250" t="n">
-        <v>0.07133473302289858</v>
+        <v>0.08007870764003557</v>
       </c>
     </row>
   </sheetData>
@@ -7225,75 +7237,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7329,13 +7341,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7371,13 +7383,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7413,13 +7425,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7455,13 +7467,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7497,13 +7509,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7539,13 +7551,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7581,13 +7593,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7623,13 +7635,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7656,7 +7668,7 @@
       <c r="I10" t="n">
         <v>1.61</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="K10" t="n">
@@ -7669,13 +7681,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7702,7 +7714,7 @@
       <c r="I11" t="n">
         <v>1.72</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="K11" t="n">
@@ -7715,13 +7727,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7748,7 +7760,7 @@
       <c r="I12" t="n">
         <v>1.78</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="K12" t="n">
@@ -7761,13 +7773,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40854</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7794,7 +7806,7 @@
       <c r="I13" t="n">
         <v>1.62</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40854</v>
       </c>
       <c r="K13" t="n">
@@ -7807,13 +7819,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7840,7 +7852,7 @@
       <c r="I14" t="n">
         <v>1.59</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K14" t="n">
@@ -7853,13 +7865,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7886,7 +7898,7 @@
       <c r="I15" t="n">
         <v>1.46</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="K15" t="n">
@@ -7899,13 +7911,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7932,7 +7944,7 @@
       <c r="I16" t="n">
         <v>1.27</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="K16" t="n">
@@ -7945,13 +7957,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7978,7 +7990,7 @@
       <c r="I17" t="n">
         <v>1.49</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="K17" t="n">
@@ -7991,13 +8003,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8024,7 +8036,7 @@
       <c r="I18" t="n">
         <v>1.48</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="K18" t="n">
@@ -8037,13 +8049,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8070,7 +8082,7 @@
       <c r="I19" t="n">
         <v>1.57</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K19" t="n">
@@ -8083,13 +8095,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8116,7 +8128,7 @@
       <c r="I20" t="n">
         <v>1.92</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="K20" t="n">
@@ -8129,13 +8141,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41590</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8162,7 +8174,7 @@
       <c r="I21" t="n">
         <v>1.85</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41590</v>
       </c>
       <c r="K21" t="n">
@@ -8175,13 +8187,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8208,7 +8220,7 @@
       <c r="I22" t="n">
         <v>1.93</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="K22" t="n">
@@ -8221,13 +8233,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41771</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8254,7 +8266,7 @@
       <c r="I23" t="n">
         <v>1.96</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41771</v>
       </c>
       <c r="K23" t="n">
@@ -8267,13 +8279,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8300,7 +8312,7 @@
       <c r="I24" t="n">
         <v>1.91</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="K24" t="n">
@@ -8313,13 +8325,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8346,7 +8358,7 @@
       <c r="I25" t="n">
         <v>2.02</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="K25" t="n">
@@ -8359,13 +8371,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8392,7 +8404,7 @@
       <c r="I26" t="n">
         <v>2.15</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="K26" t="n">
@@ -8405,13 +8417,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42135</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8438,7 +8450,7 @@
       <c r="I27" t="n">
         <v>2.11</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42135</v>
       </c>
       <c r="K27" t="n">
@@ -8451,13 +8463,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8484,7 +8496,7 @@
       <c r="I28" t="n">
         <v>2.24</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="K28" t="n">
@@ -8497,13 +8509,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8530,7 +8542,7 @@
       <c r="I29" t="n">
         <v>2.21</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="K29" t="n">
@@ -8543,13 +8555,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8576,7 +8588,7 @@
       <c r="I30" t="n">
         <v>2.15</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="K30" t="n">
@@ -8589,13 +8601,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8622,7 +8634,7 @@
       <c r="I31" t="n">
         <v>2.09</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K31" t="n">
@@ -8635,13 +8647,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8668,7 +8680,7 @@
       <c r="I32" t="n">
         <v>1.8</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K32" t="n">
@@ -8681,13 +8693,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8714,7 +8726,7 @@
       <c r="I33" t="n">
         <v>1.67</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K33" t="n">
@@ -8727,13 +8739,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8760,7 +8772,7 @@
       <c r="I34" t="n">
         <v>1.76</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="K34" t="n">
@@ -8773,13 +8785,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8806,7 +8818,7 @@
       <c r="I35" t="n">
         <v>2.05</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="K35" t="n">
@@ -8819,13 +8831,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8852,7 +8864,7 @@
       <c r="I36" t="n">
         <v>2.35</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="K36" t="n">
@@ -8865,13 +8877,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8898,7 +8910,7 @@
       <c r="I37" t="n">
         <v>2.390000000000001</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="K37" t="n">
@@ -8911,13 +8923,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8944,7 +8956,7 @@
       <c r="I38" t="n">
         <v>2.720000000000001</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="K38" t="n">
@@ -8957,13 +8969,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8990,7 +9002,7 @@
       <c r="I39" t="n">
         <v>3.210000000000001</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K39" t="n">
@@ -9003,13 +9015,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9036,7 +9048,7 @@
       <c r="I40" t="n">
         <v>3.77</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="K40" t="n">
@@ -9049,13 +9061,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9082,7 +9094,7 @@
       <c r="I41" t="n">
         <v>4.960000000000001</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="K41" t="n">
@@ -9095,13 +9107,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9128,7 +9140,7 @@
       <c r="I42" t="n">
         <v>4.42</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="K42" t="n">
@@ -9141,13 +9153,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9174,7 +9186,7 @@
       <c r="I43" t="n">
         <v>5.029999999999999</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="K43" t="n">
@@ -9187,13 +9199,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9220,7 +9232,7 @@
       <c r="I44" t="n">
         <v>5.5</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="K44" t="n">
@@ -9233,13 +9245,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9266,7 +9278,7 @@
       <c r="I45" t="n">
         <v>5.35</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="K45" t="n">
@@ -9279,13 +9291,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9312,7 +9324,7 @@
       <c r="I46" t="n">
         <v>6.72</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="K46" t="n">
@@ -9325,13 +9337,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9358,7 +9370,7 @@
       <c r="I47" t="n">
         <v>6.06</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="K47" t="n">
@@ -9371,13 +9383,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9404,7 +9416,7 @@
       <c r="I48" t="n">
         <v>7.44</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="K48" t="n">
@@ -9417,13 +9429,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9450,7 +9462,7 @@
       <c r="I49" t="n">
         <v>8.609999999999999</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="K49" t="n">
@@ -9463,13 +9475,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9496,7 +9508,7 @@
       <c r="I50" t="n">
         <v>9.66</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="K50" t="n">
@@ -9509,13 +9521,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9542,7 +9554,7 @@
       <c r="I51" t="n">
         <v>11</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="K51" t="n">
@@ -9555,13 +9567,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9588,7 +9600,7 @@
       <c r="I52" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="K52" t="n">
@@ -9601,13 +9613,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9634,7 +9646,7 @@
       <c r="I53" t="n">
         <v>6.9</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="K53" t="n">
@@ -9647,13 +9659,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9680,7 +9692,7 @@
       <c r="I54" t="n">
         <v>5.660000000000001</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="K54" t="n">
@@ -9693,13 +9705,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44683</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9726,7 +9738,7 @@
       <c r="I55" t="n">
         <v>3.670000000000001</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44683</v>
       </c>
       <c r="K55" t="n">
@@ -9739,13 +9751,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9772,7 +9784,7 @@
       <c r="I56" t="n">
         <v>1.390000000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="K56" t="n">
@@ -9785,13 +9797,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9818,7 +9830,7 @@
       <c r="I57" t="n">
         <v>1.400000000000001</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="K57" t="n">
@@ -9831,13 +9843,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9864,7 +9876,7 @@
       <c r="I58" t="n">
         <v>1.18</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="K58" t="n">
@@ -9877,13 +9889,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9910,7 +9922,7 @@
       <c r="I59" t="n">
         <v>1.41</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="K59" t="n">
@@ -9923,13 +9935,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9956,7 +9968,7 @@
       <c r="I60" t="n">
         <v>2.92</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="K60" t="n">
@@ -9969,13 +9981,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10002,7 +10014,7 @@
       <c r="I61" t="n">
         <v>4.61</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="K61" t="n">
@@ -10015,13 +10027,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10048,7 +10060,7 @@
       <c r="I62" t="n">
         <v>6.58</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="K62" t="n">
@@ -10061,13 +10073,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10094,7 +10106,7 @@
       <c r="I63" t="n">
         <v>9.77</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="K63" t="n">
@@ -10107,13 +10119,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10140,7 +10152,7 @@
       <c r="I64" t="n">
         <v>11.68</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="K64" t="n">
@@ -10153,13 +10165,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10186,7 +10198,7 @@
       <c r="I65" t="n">
         <v>13.76</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="K65" t="n">
@@ -10199,13 +10211,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45719</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10232,7 +10244,7 @@
       <c r="I66" t="n">
         <v>14.4</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45719</v>
       </c>
       <c r="K66" t="n">
@@ -10245,13 +10257,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10278,7 +10290,7 @@
       <c r="I67" t="n">
         <v>14.83</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="K67" t="n">
@@ -10291,13 +10303,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10324,7 +10336,7 @@
       <c r="I68" t="n">
         <v>17.75</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="K68" t="n">
@@ -10337,13 +10349,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10370,7 +10382,7 @@
       <c r="I69" t="n">
         <v>18.23</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="K69" t="n">
@@ -10383,13 +10395,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46083</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10416,7 +10428,7 @@
       <c r="I70" t="n">
         <v>19.23</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46083</v>
       </c>
       <c r="K70" t="n">
@@ -10429,13 +10441,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10462,7 +10474,7 @@
       <c r="I71" t="n">
         <v>19.66</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="K71" t="n">
@@ -10475,13 +10487,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46237</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10508,7 +10520,7 @@
       <c r="I72" t="n">
         <v>19.93</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46237</v>
       </c>
       <c r="K72" t="n">
@@ -10545,52 +10557,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="C2" t="n">
@@ -10619,10 +10631,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="C3" t="n">
@@ -10651,10 +10663,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="C4" t="n">
@@ -10683,10 +10695,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="C5" t="n">
@@ -10715,10 +10727,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="C6" t="n">
@@ -10747,10 +10759,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="C7" t="n">
@@ -10779,10 +10791,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="C8" t="n">
@@ -10811,10 +10823,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="C9" t="n">
@@ -10843,10 +10855,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="C10" t="n">
@@ -10875,10 +10887,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40854</v>
       </c>
       <c r="C11" t="n">
@@ -10907,10 +10919,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="C12" t="n">
@@ -10939,10 +10951,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="C13" t="n">
@@ -10971,10 +10983,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="C14" t="n">
@@ -11003,10 +11015,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="C15" t="n">
@@ -11035,10 +11047,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="C16" t="n">
@@ -11067,10 +11079,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="C17" t="n">
@@ -11099,10 +11111,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="C18" t="n">
@@ -11131,10 +11143,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41590</v>
       </c>
       <c r="C19" t="n">
@@ -11163,10 +11175,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="C20" t="n">
@@ -11195,10 +11207,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41771</v>
       </c>
       <c r="C21" t="n">
@@ -11227,10 +11239,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="C22" t="n">
@@ -11259,10 +11271,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="C23" t="n">
@@ -11291,10 +11303,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42034</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="C24" t="n">
@@ -11323,10 +11335,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42135</v>
       </c>
       <c r="C25" t="n">
@@ -11355,10 +11367,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C26" t="n">
@@ -11387,10 +11399,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C27" t="n">
@@ -11419,10 +11431,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="C28" t="n">
@@ -11451,10 +11463,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C29" t="n">
@@ -11483,10 +11495,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C30" t="n">
@@ -11515,10 +11527,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C31" t="n">
@@ -11547,10 +11559,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="C32" t="n">
@@ -11579,10 +11591,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="C33" t="n">
@@ -11611,10 +11623,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="C34" t="n">
@@ -11643,10 +11655,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="C35" t="n">
@@ -11675,10 +11687,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="C36" t="n">
@@ -11707,10 +11719,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C37" t="n">
@@ -11739,10 +11751,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="C38" t="n">
@@ -11771,10 +11783,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="C39" t="n">
@@ -11803,10 +11815,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="C40" t="n">
@@ -11835,10 +11847,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="C41" t="n">
@@ -11867,10 +11879,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="C42" t="n">
@@ -11899,10 +11911,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="C43" t="n">
@@ -11931,10 +11943,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="C44" t="n">
@@ -11963,10 +11975,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="C45" t="n">
@@ -11995,10 +12007,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="C46" t="n">
@@ -12027,10 +12039,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="C47" t="n">
@@ -12059,10 +12071,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="C48" t="n">
@@ -12091,10 +12103,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="C49" t="n">
@@ -12123,10 +12135,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="C50" t="n">
@@ -12155,10 +12167,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="C51" t="n">
@@ -12187,10 +12199,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="C52" t="n">
@@ -12219,10 +12231,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44683</v>
       </c>
       <c r="C53" t="n">
@@ -12251,10 +12263,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="C54" t="n">
@@ -12283,10 +12295,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="C55" t="n">
@@ -12315,10 +12327,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="C56" t="n">
@@ -12347,10 +12359,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="C57" t="n">
@@ -12379,10 +12391,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="C58" t="n">
@@ -12411,10 +12423,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="C59" t="n">
@@ -12443,10 +12455,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="C60" t="n">
@@ -12475,10 +12487,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="C61" t="n">
@@ -12507,10 +12519,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="C62" t="n">
@@ -12539,10 +12551,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45568</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="C63" t="n">
@@ -12571,10 +12583,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45719</v>
       </c>
       <c r="C64" t="n">
@@ -12603,10 +12615,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="C65" t="n">
@@ -12635,10 +12647,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="C66" t="n">
@@ -12667,10 +12679,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45932</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="C67" t="n">
@@ -12699,10 +12711,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46083</v>
       </c>
       <c r="C68" t="n">
@@ -12731,10 +12743,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46114</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="C69" t="n">
@@ -12763,10 +12775,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46205</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46237</v>
       </c>
       <c r="C70" t="n">
@@ -12813,12 +12825,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/PGR.xlsx
+++ b/salidas/empresas/PGR.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>13.63597965240479</v>
+        <v>13.63597583770752</v>
       </c>
       <c r="C2" t="n">
         <v>26.26000022888184</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>13.94883346557617</v>
+        <v>13.9488353729248</v>
       </c>
       <c r="C3" t="n">
         <v>26.86249923706055</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>13.53862762451172</v>
+        <v>13.53862857818604</v>
       </c>
       <c r="C4" t="n">
         <v>26.06500053405762</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>14.09310626983643</v>
+        <v>14.09309959411621</v>
       </c>
       <c r="C5" t="n">
         <v>27.13249969482422</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>14.20607566833496</v>
+        <v>14.20608043670654</v>
       </c>
       <c r="C6" t="n">
         <v>27.35000038146973</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>13.3690128326416</v>
+        <v>13.36901378631592</v>
       </c>
       <c r="C7" t="n">
         <v>25.70999908447266</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>12.57862758636475</v>
+        <v>12.57862663269043</v>
       </c>
       <c r="C8" t="n">
         <v>24.19000053405762</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>12.7866268157959</v>
+        <v>12.78662109375</v>
       </c>
       <c r="C9" t="n">
         <v>24.59000015258789</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>12.76542282104492</v>
+        <v>12.76542568206787</v>
       </c>
       <c r="C10" t="n">
         <v>24.54000091552734</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>12.57295322418213</v>
+        <v>12.57295799255371</v>
       </c>
       <c r="C11" t="n">
         <v>24.17000007629395</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>11.73024749755859</v>
+        <v>11.73024845123291</v>
       </c>
       <c r="C12" t="n">
         <v>22.54999923706055</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>12.06799507141113</v>
+        <v>12.06799411773682</v>
       </c>
       <c r="C14" t="n">
         <v>23.19000053405762</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>11.93789482116699</v>
+        <v>11.93789196014404</v>
       </c>
       <c r="C15" t="n">
         <v>22.94000053405762</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>11.35504913330078</v>
+        <v>11.35505104064941</v>
       </c>
       <c r="C16" t="n">
         <v>21.81999969482422</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>12.00554656982422</v>
+        <v>12.00553894042969</v>
       </c>
       <c r="C17" t="n">
         <v>23.06999969482422</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>11.99513816833496</v>
+        <v>11.99514007568359</v>
       </c>
       <c r="C18" t="n">
         <v>23.04999923706055</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>12.45308494567871</v>
+        <v>12.45308399200439</v>
       </c>
       <c r="C19" t="n">
         <v>23.93000030517578</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>10.91791820526123</v>
+        <v>10.91791439056396</v>
       </c>
       <c r="C20" t="n">
         <v>20.97999954223633</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>11.61702823638916</v>
+        <v>11.61703014373779</v>
       </c>
       <c r="C21" t="n">
         <v>20.34000015258789</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>10.56613159179688</v>
+        <v>10.56613063812256</v>
       </c>
       <c r="C23" t="n">
         <v>18.5</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>10.50901222229004</v>
+        <v>10.5090160369873</v>
       </c>
       <c r="C24" t="n">
         <v>18.39999961853027</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>10.94308567047119</v>
+        <v>10.94308185577393</v>
       </c>
       <c r="C25" t="n">
         <v>19.15999984741211</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>10.67810440063477</v>
+        <v>10.67810916900635</v>
       </c>
       <c r="C26" t="n">
         <v>18.54999923706055</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>10.55146789550781</v>
+        <v>10.55146980285645</v>
       </c>
       <c r="C27" t="n">
         <v>18.32999992370605</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>9.250520706176758</v>
+        <v>9.250521659851074</v>
       </c>
       <c r="C28" t="n">
         <v>16.06999969482422</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>10.47088050842285</v>
+        <v>10.47087669372559</v>
       </c>
       <c r="C29" t="n">
         <v>18.19000053405762</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>11.54732322692871</v>
+        <v>11.54732418060303</v>
       </c>
       <c r="C30" t="n">
         <v>20.05999946594238</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>10.77596378326416</v>
+        <v>10.77596473693848</v>
       </c>
       <c r="C31" t="n">
         <v>18.71999931335449</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>10.63205814361572</v>
+        <v>10.63205623626709</v>
       </c>
       <c r="C33" t="n">
         <v>18.46999931335449</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>10.0161247253418</v>
+        <v>10.01612377166748</v>
       </c>
       <c r="C34" t="n">
         <v>17.39999961853027</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>8.214370727539062</v>
+        <v>8.214374542236328</v>
       </c>
       <c r="C35" t="n">
         <v>14.27000045776367</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>8.52521800994873</v>
+        <v>8.525219917297363</v>
       </c>
       <c r="C37" t="n">
         <v>14.8100004196167</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>6.994019508361816</v>
+        <v>6.994017601013184</v>
       </c>
       <c r="C38" t="n">
         <v>12.14999961853027</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>6.660144805908203</v>
+        <v>6.660145282745361</v>
       </c>
       <c r="C39" t="n">
         <v>11.56999969482422</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>7.736593723297119</v>
+        <v>7.736589431762695</v>
       </c>
       <c r="C40" t="n">
         <v>13.4399995803833</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>8.795768737792969</v>
+        <v>8.795766830444336</v>
       </c>
       <c r="C41" t="n">
         <v>15.27999973297119</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>9.285060882568359</v>
+        <v>9.285059928894043</v>
       </c>
       <c r="C42" t="n">
         <v>16.1299991607666</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>8.697907447814941</v>
+        <v>8.697910308837891</v>
       </c>
       <c r="C43" t="n">
         <v>15.10999965667725</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>9.509561538696289</v>
+        <v>9.509560585021973</v>
       </c>
       <c r="C45" t="n">
         <v>16.52000045776367</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>9.544100761413574</v>
+        <v>9.544098854064941</v>
       </c>
       <c r="C46" t="n">
         <v>16.57999992370605</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>9.210229873657227</v>
+        <v>9.210227966308594</v>
       </c>
       <c r="C47" t="n">
         <v>16</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>9.653470039367676</v>
+        <v>9.653472900390625</v>
       </c>
       <c r="C48" t="n">
         <v>16.77000045776367</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>10.35574722290039</v>
+        <v>10.35575008392334</v>
       </c>
       <c r="C49" t="n">
         <v>17.98999977111816</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>9.63594913482666</v>
+        <v>9.635951042175293</v>
       </c>
       <c r="C50" t="n">
         <v>16.57999992370605</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>11.09471130371094</v>
+        <v>11.09471035003662</v>
       </c>
       <c r="C52" t="n">
         <v>19.09000015258789</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>11.67588901519775</v>
+        <v>11.67589282989502</v>
       </c>
       <c r="C53" t="n">
         <v>20.09000015258789</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>10.87967491149902</v>
+        <v>10.87967300415039</v>
       </c>
       <c r="C55" t="n">
         <v>18.71999931335449</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>11.41436195373535</v>
+        <v>11.41436100006104</v>
       </c>
       <c r="C56" t="n">
         <v>19.63999938964844</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>12.1292142868042</v>
+        <v>12.12920761108398</v>
       </c>
       <c r="C58" t="n">
         <v>20.8700008392334</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>12.29775524139404</v>
+        <v>12.29775238037109</v>
       </c>
       <c r="C59" t="n">
         <v>21.15999984741211</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>11.8211841583252</v>
+        <v>11.82118606567383</v>
       </c>
       <c r="C60" t="n">
         <v>20.34000015258789</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>12.13274002075195</v>
+        <v>12.13274192810059</v>
       </c>
       <c r="C61" t="n">
         <v>19.8700008392334</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>12.97955799102783</v>
+        <v>12.97955513000488</v>
       </c>
       <c r="C63" t="n">
         <v>20.82999992370605</v>
@@ -1790,7 +1790,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>13.16648960113525</v>
+        <v>13.16649150848389</v>
       </c>
       <c r="C64" t="n">
         <v>21.1299991607666</v>
@@ -1819,7 +1819,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>13.67121982574463</v>
+        <v>13.67122173309326</v>
       </c>
       <c r="C65" t="n">
         <v>21.94000053405762</v>
@@ -1848,7 +1848,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>13.49051570892334</v>
+        <v>13.49051475524902</v>
       </c>
       <c r="C66" t="n">
         <v>21.64999961853027</v>
@@ -1877,7 +1877,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>13.32227802276611</v>
+        <v>13.32227611541748</v>
       </c>
       <c r="C67" t="n">
         <v>21.3799991607666</v>
@@ -1906,7 +1906,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>12.26297473907471</v>
+        <v>12.26297187805176</v>
       </c>
       <c r="C68" t="n">
         <v>19.68000030517578</v>
@@ -1935,7 +1935,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>11.95141696929932</v>
+        <v>11.95141124725342</v>
       </c>
       <c r="C69" t="n">
         <v>19.18000030517578</v>
@@ -1964,7 +1964,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>11.06658554077148</v>
+        <v>11.0665864944458</v>
       </c>
       <c r="C70" t="n">
         <v>17.76000022888184</v>
@@ -1993,7 +1993,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>11.84548282623291</v>
+        <v>11.84548377990723</v>
       </c>
       <c r="C71" t="n">
         <v>19.01000022888184</v>
@@ -2022,7 +2022,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>11.75201416015625</v>
+        <v>11.75201988220215</v>
       </c>
       <c r="C72" t="n">
         <v>18.86000061035156</v>
@@ -2051,7 +2051,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>12.1570463180542</v>
+        <v>12.15704250335693</v>
       </c>
       <c r="C73" t="n">
         <v>19.51000022888184</v>
@@ -2080,7 +2080,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>12.89041519165039</v>
+        <v>12.89041423797607</v>
       </c>
       <c r="C74" t="n">
         <v>20.28000068664551</v>
@@ -2109,7 +2109,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>13.61502265930176</v>
+        <v>13.61502742767334</v>
       </c>
       <c r="C75" t="n">
         <v>21.42000007629395</v>
@@ -2138,7 +2138,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>14.73371982574463</v>
+        <v>14.73371887207031</v>
       </c>
       <c r="C76" t="n">
         <v>23.18000030517578</v>
@@ -2167,7 +2167,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>13.53874778747559</v>
+        <v>13.53875064849854</v>
       </c>
       <c r="C77" t="n">
         <v>21.29999923706055</v>
@@ -2196,7 +2196,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>13.81206703186035</v>
+        <v>13.81206798553467</v>
       </c>
       <c r="C78" t="n">
         <v>21.72999954223633</v>
@@ -2225,7 +2225,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>13.24000549316406</v>
+        <v>13.2400074005127</v>
       </c>
       <c r="C79" t="n">
         <v>20.82999992370605</v>
@@ -2254,7 +2254,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>12.54717922210693</v>
+        <v>12.54718208312988</v>
       </c>
       <c r="C80" t="n">
         <v>19.73999977111816</v>
@@ -2283,7 +2283,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>12.41370010375977</v>
+        <v>12.41370105743408</v>
       </c>
       <c r="C81" t="n">
         <v>19.53000068664551</v>
@@ -2312,7 +2312,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>13.18279838562012</v>
+        <v>13.18280029296875</v>
       </c>
       <c r="C82" t="n">
         <v>20.73999977111816</v>
@@ -2341,7 +2341,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>14.17437553405762</v>
+        <v>14.17437267303467</v>
       </c>
       <c r="C83" t="n">
         <v>22.29999923706055</v>
@@ -2399,7 +2399,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>14.03397846221924</v>
+        <v>14.03397560119629</v>
       </c>
       <c r="C85" t="n">
         <v>21.10000038146973</v>
@@ -2428,7 +2428,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>15.14658164978027</v>
+        <v>15.14658260345459</v>
       </c>
       <c r="C86" t="n">
         <v>22.48999977111816</v>
@@ -2457,7 +2457,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>16.40599250793457</v>
+        <v>16.40599060058594</v>
       </c>
       <c r="C87" t="n">
         <v>24.36000061035156</v>
@@ -2486,7 +2486,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>17.01885795593262</v>
+        <v>17.01885986328125</v>
       </c>
       <c r="C88" t="n">
         <v>25.27000045776367</v>
@@ -2515,7 +2515,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>17.03232765197754</v>
+        <v>17.03233337402344</v>
       </c>
       <c r="C89" t="n">
         <v>25.29000091552734</v>
@@ -2544,7 +2544,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>17.16702461242676</v>
+        <v>17.16703033447266</v>
       </c>
       <c r="C90" t="n">
         <v>25.48999977111816</v>
@@ -2602,7 +2602,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>17.51723289489746</v>
+        <v>17.51723480224609</v>
       </c>
       <c r="C92" t="n">
         <v>26.01000022888184</v>
@@ -2631,7 +2631,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>16.8841609954834</v>
+        <v>16.88416290283203</v>
       </c>
       <c r="C93" t="n">
         <v>25.06999969482422</v>
@@ -2660,7 +2660,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>18.3388843536377</v>
+        <v>18.3388786315918</v>
       </c>
       <c r="C94" t="n">
         <v>27.22999954223633</v>
@@ -2689,7 +2689,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>17.49029922485352</v>
+        <v>17.49029350280762</v>
       </c>
       <c r="C95" t="n">
         <v>25.96999931335449</v>
@@ -2718,7 +2718,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>18.81031608581543</v>
+        <v>18.8103199005127</v>
       </c>
       <c r="C96" t="n">
         <v>27.93000030517578</v>
@@ -2747,7 +2747,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>18.36581993103027</v>
+        <v>18.36581802368164</v>
       </c>
       <c r="C97" t="n">
         <v>27.27000045776367</v>
@@ -2776,7 +2776,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>16.6543083190918</v>
+        <v>16.65431022644043</v>
       </c>
       <c r="C98" t="n">
         <v>23.23999977111816</v>
@@ -2805,7 +2805,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>17.55008888244629</v>
+        <v>17.55009269714355</v>
       </c>
       <c r="C99" t="n">
         <v>24.48999977111816</v>
@@ -2834,7 +2834,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>17.35659599304199</v>
+        <v>17.35659980773926</v>
       </c>
       <c r="C100" t="n">
         <v>24.21999931335449</v>
@@ -2863,7 +2863,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>17.37809753417969</v>
+        <v>17.37809944152832</v>
       </c>
       <c r="C101" t="n">
         <v>24.25</v>
@@ -2921,7 +2921,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>18.17355346679688</v>
+        <v>18.17355155944824</v>
       </c>
       <c r="C103" t="n">
         <v>25.36000061035156</v>
@@ -2950,7 +2950,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>16.79763221740723</v>
+        <v>16.79763984680176</v>
       </c>
       <c r="C104" t="n">
         <v>23.44000053405762</v>
@@ -2979,7 +2979,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>17.92989921569824</v>
+        <v>17.92989349365234</v>
       </c>
       <c r="C105" t="n">
         <v>25.02000045776367</v>
@@ -3008,7 +3008,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>18.11622619628906</v>
+        <v>18.1162166595459</v>
       </c>
       <c r="C106" t="n">
         <v>25.28000068664551</v>
@@ -3066,7 +3066,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>19.52079772949219</v>
+        <v>19.52079582214355</v>
       </c>
       <c r="C108" t="n">
         <v>27.23999977111816</v>
@@ -3095,7 +3095,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>19.34164237976074</v>
+        <v>19.34164810180664</v>
       </c>
       <c r="C109" t="n">
         <v>26.98999977111816</v>
@@ -3124,7 +3124,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>18.59635543823242</v>
+        <v>18.59635734558105</v>
       </c>
       <c r="C110" t="n">
         <v>25.95000076293945</v>
@@ -3182,7 +3182,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>20.02140617370605</v>
+        <v>20.02140808105469</v>
       </c>
       <c r="C112" t="n">
         <v>27.20000076293945</v>
@@ -3211,7 +3211,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>19.62392997741699</v>
+        <v>19.62392234802246</v>
       </c>
       <c r="C113" t="n">
         <v>26.65999984741211</v>
@@ -3269,7 +3269,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>20.48513984680176</v>
+        <v>20.48513793945312</v>
       </c>
       <c r="C115" t="n">
         <v>27.82999992370605</v>
@@ -3298,7 +3298,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>22.45047569274902</v>
+        <v>22.45047950744629</v>
       </c>
       <c r="C116" t="n">
         <v>30.5</v>
@@ -3327,7 +3327,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>22.0529899597168</v>
+        <v>22.05299377441406</v>
       </c>
       <c r="C117" t="n">
         <v>29.95999908447266</v>
@@ -3356,7 +3356,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>22.55352592468262</v>
+        <v>22.55353164672852</v>
       </c>
       <c r="C118" t="n">
         <v>30.63999938964844</v>
@@ -3385,7 +3385,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>24.38637924194336</v>
+        <v>24.3863697052002</v>
       </c>
       <c r="C119" t="n">
         <v>33.13000106811523</v>
@@ -3414,7 +3414,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>22.68602180480957</v>
+        <v>22.68602561950684</v>
       </c>
       <c r="C120" t="n">
         <v>30.81999969482422</v>
@@ -3443,7 +3443,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>23.40738487243652</v>
+        <v>23.40737915039062</v>
       </c>
       <c r="C121" t="n">
         <v>31.79999923706055</v>
@@ -3472,7 +3472,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>23.00253677368164</v>
+        <v>23.00254058837891</v>
       </c>
       <c r="C122" t="n">
         <v>31.25</v>
@@ -3501,7 +3501,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>24.18289566040039</v>
+        <v>24.18289375305176</v>
       </c>
       <c r="C123" t="n">
         <v>31.92000007629395</v>
@@ -3530,7 +3530,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>26.62239456176758</v>
+        <v>26.62239646911621</v>
       </c>
       <c r="C124" t="n">
         <v>35.13999938964844</v>
@@ -3559,7 +3559,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>24.69806480407715</v>
+        <v>24.69806861877441</v>
       </c>
       <c r="C125" t="n">
         <v>32.59999847412109</v>
@@ -3617,7 +3617,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>25.37991333007812</v>
+        <v>25.37992095947266</v>
       </c>
       <c r="C127" t="n">
         <v>33.5</v>
@@ -3646,7 +3646,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>24.6298828125</v>
+        <v>24.62988471984863</v>
       </c>
       <c r="C128" t="n">
         <v>32.5099983215332</v>
@@ -3704,7 +3704,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>23.86469650268555</v>
+        <v>23.86470031738281</v>
       </c>
       <c r="C130" t="n">
         <v>31.5</v>
@@ -3733,7 +3733,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>23.87227630615234</v>
+        <v>23.87226867675781</v>
       </c>
       <c r="C131" t="n">
         <v>31.51000022888184</v>
@@ -3791,7 +3791,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>26.89513969421387</v>
+        <v>26.89513397216797</v>
       </c>
       <c r="C133" t="n">
         <v>35.5</v>
@@ -3820,7 +3820,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>28.36489677429199</v>
+        <v>28.36490058898926</v>
       </c>
       <c r="C134" t="n">
         <v>37.43999862670898</v>
@@ -3849,7 +3849,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>30.23304557800293</v>
+        <v>30.23305511474609</v>
       </c>
       <c r="C135" t="n">
         <v>39.18000030517578</v>
@@ -3878,7 +3878,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>30.23304557800293</v>
+        <v>30.23305511474609</v>
       </c>
       <c r="C136" t="n">
         <v>39.18000030517578</v>
@@ -3907,7 +3907,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>30.64974021911621</v>
+        <v>30.64973449707031</v>
       </c>
       <c r="C137" t="n">
         <v>39.72000122070312</v>
@@ -3936,7 +3936,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>32.74090957641602</v>
+        <v>32.74089431762695</v>
       </c>
       <c r="C138" t="n">
         <v>42.43000030517578</v>
@@ -3965,7 +3965,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>34.02183151245117</v>
+        <v>34.02182388305664</v>
       </c>
       <c r="C139" t="n">
         <v>44.09000015258789</v>
@@ -4023,7 +4023,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>35.86605453491211</v>
+        <v>35.86606216430664</v>
       </c>
       <c r="C141" t="n">
         <v>46.47999954223633</v>
@@ -4052,7 +4052,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>37.36305236816406</v>
+        <v>37.36305618286133</v>
       </c>
       <c r="C142" t="n">
         <v>48.41999816894531</v>
@@ -4139,7 +4139,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>43.45904922485352</v>
+        <v>43.45904541015625</v>
       </c>
       <c r="C145" t="n">
         <v>56.31999969482422</v>
@@ -4168,7 +4168,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>41.74597930908203</v>
+        <v>41.74600601196289</v>
       </c>
       <c r="C146" t="n">
         <v>54.09999847412109</v>
@@ -4226,7 +4226,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>48.01478576660156</v>
+        <v>48.01478958129883</v>
       </c>
       <c r="C148" t="n">
         <v>60.93000030517578</v>
@@ -4255,7 +4255,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>47.51044464111328</v>
+        <v>47.51045227050781</v>
       </c>
       <c r="C149" t="n">
         <v>60.29000091552734</v>
@@ -4284,7 +4284,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>48.92890548706055</v>
+        <v>48.92890167236328</v>
       </c>
       <c r="C150" t="n">
         <v>62.09000015258789</v>
@@ -4313,7 +4313,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>46.61209106445312</v>
+        <v>46.61209487915039</v>
       </c>
       <c r="C151" t="n">
         <v>59.15000152587891</v>
@@ -4342,7 +4342,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>47.28980255126953</v>
+        <v>47.289794921875</v>
       </c>
       <c r="C152" t="n">
         <v>60.0099983215332</v>
@@ -4371,7 +4371,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>53.21580505371094</v>
+        <v>53.21579360961914</v>
       </c>
       <c r="C153" t="n">
         <v>67.52999877929688</v>
@@ -4400,7 +4400,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>55.98179244995117</v>
+        <v>55.98178100585938</v>
       </c>
       <c r="C154" t="n">
         <v>71.04000091552734</v>
@@ -4429,7 +4429,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>54.92582702636719</v>
+        <v>54.92583084106445</v>
       </c>
       <c r="C155" t="n">
         <v>69.69999694824219</v>
@@ -4458,7 +4458,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>52.2386360168457</v>
+        <v>52.23863983154297</v>
       </c>
       <c r="C156" t="n">
         <v>66.29000091552734</v>
@@ -4487,7 +4487,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>47.54196166992188</v>
+        <v>47.54197692871094</v>
       </c>
       <c r="C157" t="n">
         <v>60.33000183105469</v>
@@ -4516,7 +4516,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>53.02666854858398</v>
+        <v>53.02666473388672</v>
       </c>
       <c r="C158" t="n">
         <v>67.29000091552734</v>
@@ -4545,7 +4545,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>59.67710113525391</v>
+        <v>59.67708969116211</v>
       </c>
       <c r="C159" t="n">
         <v>72.90000152587891</v>
@@ -4574,7 +4574,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>59.01402282714844</v>
+        <v>59.0140266418457</v>
       </c>
       <c r="C160" t="n">
         <v>72.08999633789062</v>
@@ -4603,7 +4603,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>64.06254577636719</v>
+        <v>64.06256103515625</v>
       </c>
       <c r="C161" t="n">
         <v>78.15000152587891</v>
@@ -4632,7 +4632,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>64.98887634277344</v>
+        <v>64.98886108398438</v>
       </c>
       <c r="C162" t="n">
         <v>79.27999877929688</v>
@@ -4661,7 +4661,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>65.52169036865234</v>
+        <v>65.52170562744141</v>
       </c>
       <c r="C163" t="n">
         <v>79.93000030517578</v>
@@ -4690,7 +4690,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>66.46284484863281</v>
+        <v>66.46285247802734</v>
       </c>
       <c r="C164" t="n">
         <v>80.98000335693359</v>
@@ -4719,7 +4719,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>62.21146774291992</v>
+        <v>62.21146011352539</v>
       </c>
       <c r="C165" t="n">
         <v>75.80000305175781</v>
@@ -4748,7 +4748,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>63.40151214599609</v>
+        <v>63.40150833129883</v>
       </c>
       <c r="C166" t="n">
         <v>77.25</v>
@@ -4777,7 +4777,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>57.28097534179688</v>
+        <v>57.28097915649414</v>
       </c>
       <c r="C167" t="n">
         <v>69.69999694824219</v>
@@ -4806,7 +4806,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>60.03407287597656</v>
+        <v>60.03408432006836</v>
       </c>
       <c r="C168" t="n">
         <v>73.05000305175781</v>
@@ -4835,7 +4835,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>59.49167251586914</v>
+        <v>59.49166870117188</v>
       </c>
       <c r="C169" t="n">
         <v>72.38999938964844</v>
@@ -4893,7 +4893,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>62.05154800415039</v>
+        <v>62.05154037475586</v>
       </c>
       <c r="C171" t="n">
         <v>73.16000366210938</v>
@@ -4922,7 +4922,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>62.6282958984375</v>
+        <v>62.6282844543457</v>
       </c>
       <c r="C172" t="n">
         <v>73.83999633789062</v>
@@ -4951,7 +4951,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>65.64939880371094</v>
+        <v>65.64939117431641</v>
       </c>
       <c r="C173" t="n">
         <v>77.30000305175781</v>
@@ -4980,7 +4980,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>65.97209930419922</v>
+        <v>65.97210693359375</v>
       </c>
       <c r="C174" t="n">
         <v>77.68000030517578</v>
@@ -5038,7 +5038,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>76.82096099853516</v>
+        <v>76.82098388671875</v>
       </c>
       <c r="C176" t="n">
         <v>90.33999633789062</v>
@@ -5067,7 +5067,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>80.81761169433594</v>
+        <v>80.81761932373047</v>
       </c>
       <c r="C177" t="n">
         <v>95.04000091552734</v>
@@ -5096,7 +5096,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>80.50300598144531</v>
+        <v>80.50298309326172</v>
       </c>
       <c r="C178" t="n">
         <v>94.66999816894531</v>
@@ -5125,7 +5125,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>78.22901153564453</v>
+        <v>78.22900390625</v>
       </c>
       <c r="C179" t="n">
         <v>91.90000152587891</v>
@@ -5154,7 +5154,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>74.15157318115234</v>
+        <v>74.15158081054688</v>
       </c>
       <c r="C180" t="n">
         <v>87.11000061035156</v>
@@ -5183,7 +5183,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>84.17066955566406</v>
+        <v>84.17068481445312</v>
       </c>
       <c r="C181" t="n">
         <v>98.87999725341797</v>
@@ -5212,7 +5212,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>77.84437561035156</v>
+        <v>77.84439086914062</v>
       </c>
       <c r="C182" t="n">
         <v>87.19000244140625</v>
@@ -5241,7 +5241,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>76.73728179931641</v>
+        <v>76.73729705810547</v>
       </c>
       <c r="C183" t="n">
         <v>85.94999694824219</v>
@@ -5270,7 +5270,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>85.36183929443359</v>
+        <v>85.36186218261719</v>
       </c>
       <c r="C184" t="n">
         <v>95.61000061035156</v>
@@ -5299,7 +5299,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>90.03507232666016</v>
+        <v>90.03508758544922</v>
       </c>
       <c r="C185" t="n">
         <v>100.7399978637695</v>
@@ -5357,7 +5357,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>87.77392578125</v>
+        <v>87.77394866943359</v>
       </c>
       <c r="C187" t="n">
         <v>98.20999908447266</v>
@@ -5386,7 +5386,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>85.13405609130859</v>
+        <v>85.13407135009766</v>
       </c>
       <c r="C188" t="n">
         <v>95.16000366210938</v>
@@ -5415,7 +5415,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>86.18973541259766</v>
+        <v>86.18972015380859</v>
       </c>
       <c r="C189" t="n">
         <v>96.33999633789062</v>
@@ -5444,7 +5444,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>80.86662292480469</v>
+        <v>80.86660766601562</v>
       </c>
       <c r="C190" t="n">
         <v>90.38999938964844</v>
@@ -5473,7 +5473,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>84.97665405273438</v>
+        <v>84.97666168212891</v>
       </c>
       <c r="C191" t="n">
         <v>94.87999725341797</v>
@@ -5502,7 +5502,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>83.23915863037109</v>
+        <v>83.23914337158203</v>
       </c>
       <c r="C192" t="n">
         <v>92.94000244140625</v>
@@ -5531,7 +5531,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>93.29402160644531</v>
+        <v>93.29404449462891</v>
       </c>
       <c r="C193" t="n">
         <v>102.6500015258789</v>
@@ -5589,7 +5589,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>96.36873626708984</v>
+        <v>96.36875152587891</v>
       </c>
       <c r="C195" t="n">
         <v>105.9300003051758</v>
@@ -5618,7 +5618,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>103.7012557983398</v>
+        <v>103.7012481689453</v>
       </c>
       <c r="C196" t="n">
         <v>113.9899978637695</v>
@@ -5647,7 +5647,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>97.7552490234375</v>
+        <v>97.75524139404297</v>
       </c>
       <c r="C197" t="n">
         <v>107.3600006103516</v>
@@ -5705,7 +5705,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>105.8681259155273</v>
+        <v>105.8681335449219</v>
       </c>
       <c r="C199" t="n">
         <v>116.2699966430664</v>
@@ -5763,7 +5763,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>111.7727813720703</v>
+        <v>111.7727966308594</v>
       </c>
       <c r="C201" t="n">
         <v>122.6500015258789</v>
@@ -5792,7 +5792,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>105.9039154052734</v>
+        <v>105.9039077758789</v>
       </c>
       <c r="C202" t="n">
         <v>116.2099990844727</v>
@@ -5821,7 +5821,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>117.1085433959961</v>
+        <v>117.1085586547852</v>
       </c>
       <c r="C203" t="n">
         <v>128.3999938964844</v>
@@ -5850,7 +5850,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>120.5287933349609</v>
+        <v>120.5287704467773</v>
       </c>
       <c r="C204" t="n">
         <v>132.1499938964844</v>
@@ -5879,7 +5879,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>118.303352355957</v>
+        <v>118.3033676147461</v>
       </c>
       <c r="C205" t="n">
         <v>129.7100067138672</v>
@@ -5908,7 +5908,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>124.4542770385742</v>
+        <v>124.4542694091797</v>
       </c>
       <c r="C206" t="n">
         <v>136.3500061035156</v>
@@ -5937,7 +5937,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>130.9987487792969</v>
+        <v>130.9987182617188</v>
       </c>
       <c r="C207" t="n">
         <v>143.5200042724609</v>
@@ -5966,7 +5966,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>130.5788879394531</v>
+        <v>130.5789031982422</v>
       </c>
       <c r="C208" t="n">
         <v>143.0599975585938</v>
@@ -5995,7 +5995,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>124.5862731933594</v>
+        <v>124.5862579345703</v>
       </c>
       <c r="C209" t="n">
         <v>136.3999938964844</v>
@@ -6024,7 +6024,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>116.8316116333008</v>
+        <v>116.8315963745117</v>
       </c>
       <c r="C210" t="n">
         <v>127.9100036621094</v>
@@ -6053,7 +6053,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>120.9053039550781</v>
+        <v>120.9053115844727</v>
       </c>
       <c r="C211" t="n">
         <v>132.3699951171875</v>
@@ -6082,7 +6082,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>115.156364440918</v>
+        <v>115.156379699707</v>
       </c>
       <c r="C212" t="n">
         <v>125.9800033569336</v>
@@ -6111,7 +6111,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>122.0028533935547</v>
+        <v>122.0028686523438</v>
       </c>
       <c r="C213" t="n">
         <v>133.4700012207031</v>
@@ -6140,7 +6140,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>127.3319625854492</v>
+        <v>127.3319931030273</v>
       </c>
       <c r="C214" t="n">
         <v>139.3000030517578</v>
@@ -6169,7 +6169,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>144.611328125</v>
+        <v>144.6113433837891</v>
       </c>
       <c r="C215" t="n">
         <v>158.0899963378906</v>
@@ -6198,7 +6198,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>150.0449523925781</v>
+        <v>150.044921875</v>
       </c>
       <c r="C216" t="n">
         <v>164.0299987792969</v>
@@ -6227,7 +6227,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>145.6998596191406</v>
+        <v>145.6998748779297</v>
       </c>
       <c r="C217" t="n">
         <v>159.2799987792969</v>
@@ -6256,7 +6256,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>163.8724212646484</v>
+        <v>163.8724365234375</v>
       </c>
       <c r="C218" t="n">
         <v>178.25</v>
@@ -6285,7 +6285,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>174.2701416015625</v>
+        <v>174.2701721191406</v>
       </c>
       <c r="C219" t="n">
         <v>189.5599975585938</v>
@@ -6314,7 +6314,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>190.1379699707031</v>
+        <v>190.1379547119141</v>
       </c>
       <c r="C220" t="n">
         <v>206.8200073242188</v>
@@ -6343,7 +6343,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>191.5438232421875</v>
+        <v>191.5438079833984</v>
       </c>
       <c r="C221" t="n">
         <v>208.25</v>
@@ -6401,7 +6401,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>191.0471801757812</v>
+        <v>191.0471649169922</v>
       </c>
       <c r="C223" t="n">
         <v>207.7100067138672</v>
@@ -6430,7 +6430,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>197.0362396240234</v>
+        <v>197.0362548828125</v>
       </c>
       <c r="C224" t="n">
         <v>214.1199951171875</v>
@@ -6459,7 +6459,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>232.0780334472656</v>
+        <v>232.0780029296875</v>
       </c>
       <c r="C225" t="n">
         <v>252.1999969482422</v>
@@ -6488,7 +6488,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>233.5135345458984</v>
+        <v>233.5135192871094</v>
       </c>
       <c r="C226" t="n">
         <v>253.7599945068359</v>
@@ -6517,7 +6517,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>223.5434722900391</v>
+        <v>223.54345703125</v>
       </c>
       <c r="C227" t="n">
         <v>242.8300018310547</v>
@@ -6546,7 +6546,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>247.5244903564453</v>
+        <v>247.5244598388672</v>
       </c>
       <c r="C228" t="n">
         <v>268.8800048828125</v>
@@ -6604,7 +6604,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>231.2333984375</v>
+        <v>231.2333831787109</v>
       </c>
       <c r="C230" t="n">
         <v>246.4400024414062</v>
@@ -6633,7 +6633,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>264.5991821289062</v>
+        <v>264.5991516113281</v>
       </c>
       <c r="C231" t="n">
         <v>282</v>
@@ -6749,7 +6749,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>250.4824371337891</v>
+        <v>250.482421875</v>
       </c>
       <c r="C235" t="n">
         <v>266.8599853515625</v>
@@ -6778,7 +6778,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>227.2738494873047</v>
+        <v>227.2738342285156</v>
       </c>
       <c r="C236" t="n">
         <v>242.0399932861328</v>
@@ -6836,7 +6836,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>231.8842926025391</v>
+        <v>231.8843078613281</v>
       </c>
       <c r="C238" t="n">
         <v>246.9499969482422</v>
@@ -6894,7 +6894,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>214.9193878173828</v>
+        <v>214.9193725585938</v>
       </c>
       <c r="C240" t="n">
         <v>228.7899932861328</v>
@@ -6923,7 +6923,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>213.9142608642578</v>
+        <v>213.9142761230469</v>
       </c>
       <c r="C241" t="n">
         <v>227.7200012207031</v>
